--- a/doc/data/results.xlsx
+++ b/doc/data/results.xlsx
@@ -619,7 +619,7 @@
         <v>14</v>
       </c>
       <c r="B14" s="11" t="n">
-        <v>16</v>
+        <v>8</v>
       </c>
       <c r="E14" s="3"/>
     </row>
@@ -632,11 +632,11 @@
       </c>
       <c r="B16" s="12" t="n">
         <f aca="false">B2*$B$14*$B$14</f>
-        <v>419284.48</v>
+        <v>104821.12</v>
       </c>
       <c r="C16" s="12" t="n">
         <f aca="false">C2*$B$14*$B$14</f>
-        <v>371.2</v>
+        <v>92.8</v>
       </c>
     </row>
     <row r="17" customFormat="false" ht="17.05" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -645,11 +645,11 @@
       </c>
       <c r="B17" s="12" t="n">
         <f aca="false">B3*$B$14*$B$14</f>
-        <v>356556.8</v>
+        <v>89139.2</v>
       </c>
       <c r="C17" s="12" t="n">
         <f aca="false">C3*$B$14*$B$14</f>
-        <v>299.52</v>
+        <v>74.88</v>
       </c>
     </row>
     <row r="18" customFormat="false" ht="17.05" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -658,11 +658,11 @@
       </c>
       <c r="B18" s="12" t="n">
         <f aca="false">B4*$B$14*$B$14</f>
-        <v>464081.92</v>
+        <v>116020.48</v>
       </c>
       <c r="C18" s="12" t="n">
         <f aca="false">C4*$B$14*$B$14</f>
-        <v>394.24</v>
+        <v>98.56</v>
       </c>
     </row>
     <row r="19" customFormat="false" ht="17.05" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -671,11 +671,11 @@
       </c>
       <c r="B19" s="12" t="n">
         <f aca="false">B7*$B$14*$B$14</f>
-        <v>386135.04</v>
+        <v>96533.76</v>
       </c>
       <c r="C19" s="12" t="n">
         <f aca="false">C7*$B$14*$B$14</f>
-        <v>307.2</v>
+        <v>76.8</v>
       </c>
     </row>
     <row r="20" customFormat="false" ht="17.05" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -684,11 +684,11 @@
       </c>
       <c r="B20" s="12" t="n">
         <f aca="false">B8*$B$14*$B$14</f>
-        <v>308231.68</v>
+        <v>77057.92</v>
       </c>
       <c r="C20" s="12" t="n">
         <f aca="false">C8*$B$14*$B$14</f>
-        <v>240.384</v>
+        <v>60.096</v>
       </c>
     </row>
     <row r="21" customFormat="false" ht="17.05" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -697,11 +697,11 @@
       </c>
       <c r="B21" s="12" t="n">
         <f aca="false">(4*B10+3*B9)*$B$14</f>
-        <v>25896.48</v>
+        <v>12948.24</v>
       </c>
       <c r="C21" s="12" t="n">
         <f aca="false">(4*C10+3*C9)*$B$14</f>
-        <v>23.248</v>
+        <v>11.624</v>
       </c>
     </row>
     <row r="22" customFormat="false" ht="17.05" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -710,11 +710,11 @@
       </c>
       <c r="B22" s="12" t="n">
         <f aca="false">(4*B10)*$B$14</f>
-        <v>16435.2</v>
+        <v>8217.6</v>
       </c>
       <c r="C22" s="12" t="n">
-        <f aca="false">(4*C11+3*C10)*$B$14</f>
-        <v>22.576</v>
+        <f aca="false">(4*C10+3*C9)*$B$14</f>
+        <v>11.624</v>
       </c>
       <c r="D22" s="12"/>
     </row>
@@ -724,11 +724,11 @@
       </c>
       <c r="B23" s="12" t="n">
         <f aca="false">(4*B12)*$B$14</f>
-        <v>27154.56</v>
+        <v>13577.28</v>
       </c>
       <c r="C23" s="12" t="n">
         <f aca="false">(4*C12)*$B$14</f>
-        <v>20.096</v>
+        <v>10.048</v>
       </c>
     </row>
     <row r="24" customFormat="false" ht="17.05" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -740,11 +740,11 @@
       </c>
       <c r="B25" s="12" t="n">
         <f aca="false">B16</f>
-        <v>419284.48</v>
+        <v>104821.12</v>
       </c>
       <c r="C25" s="12" t="n">
         <f aca="false">C16</f>
-        <v>371.2</v>
+        <v>92.8</v>
       </c>
     </row>
     <row r="26" customFormat="false" ht="17.05" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -753,11 +753,11 @@
       </c>
       <c r="B26" s="12" t="n">
         <f aca="false">B17</f>
-        <v>356556.8</v>
+        <v>89139.2</v>
       </c>
       <c r="C26" s="12" t="n">
         <f aca="false">C17</f>
-        <v>299.52</v>
+        <v>74.88</v>
       </c>
     </row>
     <row r="27" customFormat="false" ht="17.05" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -766,11 +766,11 @@
       </c>
       <c r="B27" s="12" t="n">
         <f aca="false">B18</f>
-        <v>464081.92</v>
+        <v>116020.48</v>
       </c>
       <c r="C27" s="12" t="n">
         <f aca="false">C18</f>
-        <v>394.24</v>
+        <v>98.56</v>
       </c>
     </row>
     <row r="28" customFormat="false" ht="17.05" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -779,11 +779,11 @@
       </c>
       <c r="B28" s="12" t="n">
         <f aca="false">B19+B21</f>
-        <v>412031.52</v>
+        <v>109482</v>
       </c>
       <c r="C28" s="12" t="n">
         <f aca="false">C19+C21</f>
-        <v>330.448</v>
+        <v>88.424</v>
       </c>
     </row>
     <row r="29" customFormat="false" ht="17.05" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -792,11 +792,11 @@
       </c>
       <c r="B29" s="12" t="n">
         <f aca="false">B19+B22</f>
-        <v>402570.24</v>
+        <v>104751.36</v>
       </c>
       <c r="C29" s="12" t="n">
         <f aca="false">C19+C22</f>
-        <v>329.776</v>
+        <v>88.424</v>
       </c>
     </row>
     <row r="30" customFormat="false" ht="17.05" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -805,11 +805,11 @@
       </c>
       <c r="B30" s="12" t="n">
         <f aca="false">B20+B23</f>
-        <v>335386.24</v>
+        <v>90635.2</v>
       </c>
       <c r="C30" s="12" t="n">
         <f aca="false">C20+C23</f>
-        <v>260.48</v>
+        <v>70.144</v>
       </c>
     </row>
     <row r="31" customFormat="false" ht="17.05" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -834,11 +834,11 @@
       </c>
       <c r="B33" s="14" t="n">
         <f aca="false">-(B25-B28)/B25</f>
-        <v>-0.017298422302681</v>
+        <v>0.0444650848989212</v>
       </c>
       <c r="C33" s="14" t="n">
         <f aca="false">-(C25-C28)/C25</f>
-        <v>-0.109784482758621</v>
+        <v>-0.0471551724137932</v>
       </c>
     </row>
     <row r="34" customFormat="false" ht="17.05" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -847,11 +847,11 @@
       </c>
       <c r="B34" s="14" t="n">
         <f aca="false">-(B25-B29)/B25</f>
-        <v>-0.0398637221201223</v>
+        <v>-0.000665514735961558</v>
       </c>
       <c r="C34" s="14" t="n">
         <f aca="false">-(C25-C29)/C25</f>
-        <v>-0.111594827586207</v>
+        <v>-0.0471551724137932</v>
       </c>
     </row>
     <row r="35" customFormat="false" ht="17.05" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -860,11 +860,11 @@
       </c>
       <c r="B35" s="14" t="n">
         <f aca="false">-(B26-B30)/B26</f>
-        <v>-0.059375</v>
+        <v>0.0167827398047099</v>
       </c>
       <c r="C35" s="14" t="n">
         <f aca="false">-(C26-C30)/C26</f>
-        <v>-0.13034188034188</v>
+        <v>-0.0632478632478633</v>
       </c>
     </row>
     <row r="36" customFormat="false" ht="17.05" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -873,11 +873,11 @@
       </c>
       <c r="B36" s="14" t="n">
         <f aca="false">(B30-B25)/B25</f>
-        <v>-0.200098606082438</v>
+        <v>-0.135334558531716</v>
       </c>
       <c r="C36" s="14" t="n">
         <f aca="false">(C30-C25)/C25</f>
-        <v>-0.298275862068966</v>
+        <v>-0.244137931034483</v>
       </c>
     </row>
     <row r="1048575" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
